--- a/data/parts.xlsx
+++ b/data/parts.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,26 +425,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D55"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>part_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>width</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>height</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Depth</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>qty</t>
         </is>
@@ -441,142 +453,142 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BF0335</t>
+          <t>1001-KIT-WALL-762W-BT</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>76.2</v>
+        <v>726</v>
       </c>
       <c r="C2" t="n">
-        <v>889</v>
+        <v>285.8</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>V3D16-18-DR1</t>
+          <t>1001-KIT-WALL-762W-SL</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>100</v>
+        <v>762</v>
       </c>
       <c r="C3" t="n">
-        <v>427</v>
+        <v>285.8</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>V3D16-18-DL2</t>
+          <t>1001-KIT-WALL-762W-SR</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>100</v>
+        <v>762</v>
       </c>
       <c r="C4" t="n">
-        <v>427</v>
+        <v>285.8</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>V3D16-18-DF2</t>
+          <t>1001-KIT-WALL-762W-TP</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>100</v>
+        <v>726</v>
       </c>
       <c r="C5" t="n">
-        <v>345.1</v>
+        <v>285.8</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>V3D16-18-DH1</t>
+          <t>1001-KIT-WALL-762W-BK</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>100</v>
+        <v>762</v>
       </c>
       <c r="C6" t="n">
-        <v>345.1</v>
+        <v>285.8</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>V3D16-18-DL1</t>
+          <t>1001-KIT-BASE-762W-SR</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>100</v>
+        <v>876.3</v>
       </c>
       <c r="C7" t="n">
-        <v>427</v>
+        <v>590.6</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>V3D16-18-DF1</t>
+          <t>1001-KIT-BASE-762W-BK</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>100</v>
+        <v>876.3</v>
       </c>
       <c r="C8" t="n">
-        <v>345.1</v>
+        <v>590.6</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>V3D16-18-DH2</t>
+          <t>1001-KIT-BASE-762W-SL</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>100</v>
+        <v>876.3</v>
       </c>
       <c r="C9" t="n">
-        <v>345.1</v>
+        <v>590.6</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>V3D16-18-DR2</t>
+          <t>1001-KIT-BASE-914W-SL</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>100</v>
+        <v>876.3</v>
       </c>
       <c r="C10" t="n">
-        <v>427</v>
+        <v>590.6</v>
       </c>
       <c r="D10" t="n">
         <v>1</v>
@@ -585,46 +597,46 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>V3D16-18-TS1</t>
+          <t>1001-KIT-BASE-762W-DF</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>101.6</v>
+        <v>726</v>
       </c>
       <c r="C11" t="n">
-        <v>364.1</v>
+        <v>590.6</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>V2D27-18-TS2</t>
+          <t>1001-KIT-BASE-762W-KK</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>101.6</v>
+        <v>726</v>
       </c>
       <c r="C12" t="n">
-        <v>649.8</v>
+        <v>590.6</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>V2D27-18-TS1</t>
+          <t>1001-KIT-BASE-914W-SR</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>101.6</v>
+        <v>876.3</v>
       </c>
       <c r="C13" t="n">
-        <v>649.8</v>
+        <v>590.6</v>
       </c>
       <c r="D13" t="n">
         <v>1</v>
@@ -633,14 +645,14 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>V3D16-18-TS2</t>
+          <t>1001-KIT-BASE-914W-BK</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>101.6</v>
+        <v>876.3</v>
       </c>
       <c r="C14" t="n">
-        <v>364.1</v>
+        <v>590.6</v>
       </c>
       <c r="D14" t="n">
         <v>1</v>
@@ -649,14 +661,14 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>V2D27-18-DHR</t>
+          <t>1001-KIT-BASE-914W-TP</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>114.3</v>
+        <v>878.4</v>
       </c>
       <c r="C15" t="n">
-        <v>213.8</v>
+        <v>590.6</v>
       </c>
       <c r="D15" t="n">
         <v>1</v>
@@ -665,46 +677,46 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>V2D27-18-DLL</t>
+          <t>1001-KIT-BASE-762W-BT</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>114.3</v>
+        <v>726</v>
       </c>
       <c r="C16" t="n">
-        <v>351</v>
+        <v>590.6</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>V2D27-18-DLR</t>
+          <t>1001-KIT-BASE-762W-TP</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>114.3</v>
+        <v>726</v>
       </c>
       <c r="C17" t="n">
-        <v>239</v>
+        <v>590.6</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>V2D27-18-DI</t>
+          <t>1001-KIT-BASE-914W-KK</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>114.3</v>
+        <v>878.4</v>
       </c>
       <c r="C18" t="n">
-        <v>233.2</v>
+        <v>590.6</v>
       </c>
       <c r="D18" t="n">
         <v>1</v>
@@ -713,14 +725,14 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>V2D27-18-DRL</t>
+          <t>1001-KIT-BASE-914W-BT</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>114.3</v>
+        <v>878.4</v>
       </c>
       <c r="C19" t="n">
-        <v>239</v>
+        <v>590.6</v>
       </c>
       <c r="D19" t="n">
         <v>1</v>
@@ -729,14 +741,14 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>V2D27-18-DHL</t>
+          <t>1001-KIT-PANT-609W-SL</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>114.3</v>
+        <v>2133.6</v>
       </c>
       <c r="C20" t="n">
-        <v>213.8</v>
+        <v>590.6</v>
       </c>
       <c r="D20" t="n">
         <v>1</v>
@@ -745,14 +757,14 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>V2D27-18-DF1</t>
+          <t>1001-KIT-PANT-609W-SR</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>114.3</v>
+        <v>2133.6</v>
       </c>
       <c r="C21" t="n">
-        <v>630.8</v>
+        <v>590.6</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -761,14 +773,14 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>V2D27-18-DRR</t>
+          <t>1001-KIT-PANT-609W-BT</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>114.3</v>
+        <v>573.6</v>
       </c>
       <c r="C22" t="n">
-        <v>351</v>
+        <v>590.6</v>
       </c>
       <c r="D22" t="n">
         <v>1</v>
@@ -777,14 +789,14 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>V3D16-18-DH3</t>
+          <t>1001-KIT-PANT-609W-TP</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>229</v>
+        <v>573.6</v>
       </c>
       <c r="C23" t="n">
-        <v>345.1</v>
+        <v>590.6</v>
       </c>
       <c r="D23" t="n">
         <v>1</v>
@@ -793,14 +805,14 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>V2D27-18-DR</t>
+          <t>1001-KIT-PANT-609W-BK</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>229</v>
+        <v>2133.6</v>
       </c>
       <c r="C24" t="n">
-        <v>427</v>
+        <v>590.6</v>
       </c>
       <c r="D24" t="n">
         <v>1</v>
@@ -809,497 +821,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>V3D16-18-DR3</t>
+          <t>1001-KIT-PANT-609W-SH</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>229</v>
+        <v>573.6</v>
       </c>
       <c r="C25" t="n">
-        <v>427</v>
+        <v>590.6</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>V2D27-18-DH</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>229</v>
-      </c>
-      <c r="C26" t="n">
-        <v>630.8</v>
-      </c>
-      <c r="D26" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>V3D16-18-DF3</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>229</v>
-      </c>
-      <c r="C27" t="n">
-        <v>345.1</v>
-      </c>
-      <c r="D27" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>V3D16-18-DL3</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>229</v>
-      </c>
-      <c r="C28" t="n">
-        <v>427</v>
-      </c>
-      <c r="D28" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>V2D27-18-DF2</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>229</v>
-      </c>
-      <c r="C29" t="n">
-        <v>630.8</v>
-      </c>
-      <c r="D29" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>V2D27-18-DL</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>229</v>
-      </c>
-      <c r="C30" t="n">
-        <v>427</v>
-      </c>
-      <c r="D30" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>V2D27-18-DB1</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>351</v>
-      </c>
-      <c r="C31" t="n">
-        <v>600.8</v>
-      </c>
-      <c r="D31" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>V3D16-18-DD3</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>397.05</v>
-      </c>
-      <c r="C32" t="n">
-        <v>355.6</v>
-      </c>
-      <c r="D32" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>V3D16-18-DD2</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>397.05</v>
-      </c>
-      <c r="C33" t="n">
-        <v>176.3</v>
-      </c>
-      <c r="D33" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>V3D16-18-DD1</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>397.05</v>
-      </c>
-      <c r="C34" t="n">
-        <v>176.3</v>
-      </c>
-      <c r="D34" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>V3D16-18-DD1</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>397.05</v>
-      </c>
-      <c r="C35" t="n">
-        <v>176.3</v>
-      </c>
-      <c r="D35" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>V3D16-18-DD2</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>397.05</v>
-      </c>
-      <c r="C36" t="n">
-        <v>176.3</v>
-      </c>
-      <c r="D36" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>V3D16-18-DD3</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>397.05</v>
-      </c>
-      <c r="C37" t="n">
-        <v>355.6</v>
-      </c>
-      <c r="D37" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>V3D16-18-B</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>400.1</v>
-      </c>
-      <c r="C38" t="n">
-        <v>762</v>
-      </c>
-      <c r="D38" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>V3D16-18-DB3</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>427</v>
-      </c>
-      <c r="C39" t="n">
-        <v>315.1</v>
-      </c>
-      <c r="D39" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>V3D16-18-DB1</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>427</v>
-      </c>
-      <c r="C40" t="n">
-        <v>315.1</v>
-      </c>
-      <c r="D40" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>V3D16-18-DB2</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>427</v>
-      </c>
-      <c r="C41" t="n">
-        <v>315.1</v>
-      </c>
-      <c r="D41" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>V2D27-18-DB2</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>427</v>
-      </c>
-      <c r="C42" t="n">
-        <v>600.8</v>
-      </c>
-      <c r="D42" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>V3D16-18-SR</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>515.4</v>
-      </c>
-      <c r="C43" t="n">
-        <v>876.3</v>
-      </c>
-      <c r="D43" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>V2D27-18-D</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>515.4</v>
-      </c>
-      <c r="C44" t="n">
-        <v>649.8</v>
-      </c>
-      <c r="D44" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>V2D27-18-SR</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>515.4</v>
-      </c>
-      <c r="C45" t="n">
-        <v>876.3</v>
-      </c>
-      <c r="D45" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>V3D16-18-D</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>515.4</v>
-      </c>
-      <c r="C46" t="n">
-        <v>364.1</v>
-      </c>
-      <c r="D46" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>V3D16-18-SL</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>515.4</v>
-      </c>
-      <c r="C47" t="n">
-        <v>876.3</v>
-      </c>
-      <c r="D47" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>V3D16-18-SR</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>515.4</v>
-      </c>
-      <c r="C48" t="n">
-        <v>876.3</v>
-      </c>
-      <c r="D48" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>V2D27-18-SL</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>515.4</v>
-      </c>
-      <c r="C49" t="n">
-        <v>876.3</v>
-      </c>
-      <c r="D49" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>V3D16-18-SL</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>515.4</v>
-      </c>
-      <c r="C50" t="n">
-        <v>876.3</v>
-      </c>
-      <c r="D50" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>BP2235</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>554.4</v>
-      </c>
-      <c r="C51" t="n">
-        <v>889</v>
-      </c>
-      <c r="D51" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>V2D27-18-DD1</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>681</v>
-      </c>
-      <c r="C52" t="n">
-        <v>355.6</v>
-      </c>
-      <c r="D52" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>V2D27-18-DD2</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>681</v>
-      </c>
-      <c r="C53" t="n">
-        <v>355.6</v>
-      </c>
-      <c r="D53" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>V2D27-18-B</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>685.8</v>
-      </c>
-      <c r="C54" t="n">
-        <v>762</v>
-      </c>
-      <c r="D54" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>TK9</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>2438.4</v>
-      </c>
-      <c r="C55" t="n">
-        <v>111</v>
-      </c>
-      <c r="D55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
